--- a/sample 10 (1).xlsx
+++ b/sample 10 (1).xlsx
@@ -1,63 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
-  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Santosh\Documents\Google Sites Bulk Creation\gs_bulk_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216DDA94-ADAA-4309-89DE-258B9DE82EFB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>Keyword</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
   <si>
     <t>Luxury Clothes Market</t>
   </si>
   <si>
-    <t>Glass Door Merchandiser Market</t>
-  </si>
-  <si>
-    <t>Banquet Cabinet Market</t>
-  </si>
-  <si>
-    <t>Recycled Denim Market</t>
-  </si>
-  <si>
-    <t>Global Food Sensory Analysis Service Market</t>
-  </si>
-  <si>
-    <t>Baby Clothing Market</t>
-  </si>
-  <si>
-    <t>Cell Apoptosis Assay Services Market</t>
-  </si>
-  <si>
-    <t>Global Road Wrecker Market</t>
-  </si>
-  <si>
-    <t>Halal Nutraceuticals &amp; Vaccines Market</t>
-  </si>
-  <si>
-    <t>Baby Vitamins And Supplements Market</t>
-  </si>
-  <si>
-    <t>Title</t>
+    <t>Luxury Clothes Market Size, Strategic Opportunities &amp; Forecast (2026-2033)
+Market size (2024): USD 78,500 Million · Forecast (2033): USD 135,200 Million · CAGR: 6.2%</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -163,6 +139,13 @@
 &lt;h2&gt;Contact us: Mr. Ajay N&lt;/h2&gt;
 US: +1 (970)-633-3460
 Website: https://datahorizzonresearch.com/</t>
+  </si>
+  <si>
+    <t>Glass Door Merchandiser Market</t>
+  </si>
+  <si>
+    <t>Glass Door Merchandiser Market Size, Strategic Opportunities &amp; Forecast (2026-2033)
+Market size (2024): USD 12.5 Billion · Forecast (2033): USD 23.8 Billion · CAGR: 9.5%</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -275,6 +258,13 @@
 Website: https://datahorizzonresearch.com/</t>
   </si>
   <si>
+    <t>Banquet Cabinet Market</t>
+  </si>
+  <si>
+    <t>Banquet Cabinet Market Size, Strategic Opportunities &amp; Forecast (2026-2033)
+Market size (2024): USD 480 Million · Forecast (2033): USD 885 Million · CAGR: 6.8%</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 &lt;h2&gt;Banquet Cabinet Market Industry Overview&lt;/h2&gt;
 &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt;
@@ -379,6 +369,13 @@
 Website: https://datahorizzonresearch.com/</t>
   </si>
   <si>
+    <t>Recycled Denim Market</t>
+  </si>
+  <si>
+    <t>Recycled Denim Market Size, Strategic Opportunities &amp; Forecast (2026-2033)
+Market size (2024): USD 480 Million · Forecast (2033): USD 1050 Million · CAGR: 9.0%</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 &lt;h2&gt;Recycled Denim Market Industry Overview&lt;/h2&gt;
 &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt;
@@ -477,6 +474,12 @@
 Contact us: Mr. Ajay N
 US: +1 (970)-633-3460
 Website: https://datahorizzonresearch.com/</t>
+  </si>
+  <si>
+    <t>Global Food Sensory Analysis Service Market</t>
+  </si>
+  <si>
+    <t>Global Food Sensory Analysis Service Market Size, Strategic Opportunities &amp; Forecast (2026-2033) Market size (2024): USD 485 Million · Forecast (2033): USD 1050 Million · CAGR: 9.0%</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -586,6 +589,13 @@
 Website: https://datahorizzonresearch.com/</t>
   </si>
   <si>
+    <t>Baby Clothing Market</t>
+  </si>
+  <si>
+    <t>Baby Clothing Market Size, Strategic Opportunities &amp; Forecast (2026-2033)
+Market size (2024): USD 62.5 Billion · Forecast (2033): USD 105.0 Billion · CAGR: 6.0%</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 &lt;h2&gt;Baby Clothing Market Industry Overview&lt;/h2&gt;
 &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt;
@@ -691,6 +701,12 @@
 Contact us: Mr. Ajay N
 US: +1 (970)-633-3460
 Website: https://datahorizzonresearch.com/</t>
+  </si>
+  <si>
+    <t>Cell Apoptosis Assay Services Market</t>
+  </si>
+  <si>
+    <t>Cell Apoptosis Assay Services Market Size, Strategic Opportunities &amp; Forecast (2026-2033)</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -809,6 +825,12 @@
 Website: https://datahorizzonresearch.com/</t>
   </si>
   <si>
+    <t>Global Road Wrecker Market</t>
+  </si>
+  <si>
+    <t>Global Road Wrecker Market Size, Strategic Opportunities &amp; Forecast (2026-2033)</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 The Global Road Wrecker Market is poised for steady expansion, driven by infrastructure development and fleet modernization.
 Market size (2024): USD 385 Million
@@ -919,6 +941,12 @@
 Website: https://datahorizzonresearch.com/</t>
   </si>
   <si>
+    <t>Halal Nutraceuticals &amp; Vaccines Market</t>
+  </si>
+  <si>
+    <t>Halal Nutraceuticals &amp; Vaccines Market Size, Strategic Opportunities &amp; Forecast (2026-2033)</t>
+  </si>
+  <si>
     <t xml:space="preserve">
 Market size (2024): USD 1800 Million · Forecast (2033): USD 5500 Million · CAGR: 13.2%
 &lt;h2&gt;Halal Nutraceuticals &amp; Vaccines Market Industry Overview&lt;/h2&gt;
@@ -1026,6 +1054,12 @@
 Contact us: Mr. Ajay N
 US: +1 (970)-633-3460
 Website: https://datahorizzonresearch.com/</t>
+  </si>
+  <si>
+    <t>Baby Vitamins And Supplements Market</t>
+  </si>
+  <si>
+    <t>Baby Vitamins And Supplements Market Size, Strategic Opportunities &amp; Forecast (2026-2033)</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1137,53 +1171,12 @@
 US: +1 (970)-633-3460
 Website: https://datahorizzonresearch.com/</t>
   </si>
-  <si>
-    <t>Luxury Clothes Market Size, Strategic Opportunities &amp; Forecast (2026-2033)
-Market size (2024): USD 78,500 Million · Forecast (2033): USD 135,200 Million · CAGR: 6.2%</t>
-  </si>
-  <si>
-    <t>Glass Door Merchandiser Market Size, Strategic Opportunities &amp; Forecast (2026-2033)
-Market size (2024): USD 12.5 Billion · Forecast (2033): USD 23.8 Billion · CAGR: 9.5%</t>
-  </si>
-  <si>
-    <t>Banquet Cabinet Market Size, Strategic Opportunities &amp; Forecast (2026-2033)
-Market size (2024): USD 480 Million · Forecast (2033): USD 885 Million · CAGR: 6.8%</t>
-  </si>
-  <si>
-    <t>Recycled Denim Market Size, Strategic Opportunities &amp; Forecast (2026-2033)
-Market size (2024): USD 480 Million · Forecast (2033): USD 1050 Million · CAGR: 9.0%</t>
-  </si>
-  <si>
-    <t>Global Food Sensory Analysis Service Market Size, Strategic Opportunities &amp; Forecast (2026-2033) Market size (2024): USD 485 Million · Forecast (2033): USD 1050 Million · CAGR: 9.0%</t>
-  </si>
-  <si>
-    <t>Baby Clothing Market Size, Strategic Opportunities &amp; Forecast (2026-2033)
-Market size (2024): USD 62.5 Billion · Forecast (2033): USD 105.0 Billion · CAGR: 6.0%</t>
-  </si>
-  <si>
-    <t>Cell Apoptosis Assay Services Market Size, Strategic Opportunities &amp; Forecast (2026-2033)</t>
-  </si>
-  <si>
-    <t>Global Road Wrecker Market Size, Strategic Opportunities &amp; Forecast (2026-2033)</t>
-  </si>
-  <si>
-    <t>Halal Nutraceuticals &amp; Vaccines Market Size, Strategic Opportunities &amp; Forecast (2026-2033)</t>
-  </si>
-  <si>
-    <t>Baby Vitamins And Supplements Market Size, Strategic Opportunities &amp; Forecast (2026-2033)</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>Keyword</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1201,13 +1194,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1220,14 +1207,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1236,10 +1215,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1374,6 +1353,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -1400,24 +1380,25 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1478,164 +1459,156 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="41.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.26953125" customWidth="1"/>
-    <col min="3" max="5" width="40.26953125" customWidth="1"/>
+    <col min="1" max="1" width="41.26953" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.26953" customWidth="1"/>
+    <col min="3" max="5" width="40.26953" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
-        <v>31</v>
+      <c r="C4" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="5">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C6" t="s">
-        <v>15</v>
+      <c r="C9" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/luxury-clothes-market-53600" display="&lt;h2&gt;Luxury Clothes Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 78,500 Million · Forecast (2033): USD 135,200 Million · CAGR: 6.2%  &lt;h2&gt;Luxury Clothes Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Luxury Clothes Market encompasses high-end apparel and accessories characterized by superior craftsmanship, exclusive designs, premium materials, and brand prestige. This sector caters to discerning consumers seeking exclusivity, quality, and status. Its current relevance is amplified by rising disposable incomes globally, particularly in emerging economies, and a growing consumer appreciation for sustainable and ethically produced goods. Technological evolution, including advanced manufacturing techniques and digital design, is enhancing product innovation and customization. End-use significance extends beyond personal adornment, influencing fashion trends, cultural expression, and serving as an investment for some consumers. The market thrives on brand heritage, aspirational marketing, and an evolving definition of luxury that now often includes digital and experiential elements.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/luxury-clothes-market-53600&lt;/h2&gt;  &lt;h2&gt;Luxury Clothes Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Luxury Clothes Market has demonstrated robust historical performance, navigating global economic shifts with resilience. From 2019 to 2024, the market experienced steady growth, punctuated by a brief dip during the pandemic, followed by a strong rebound driven by pent-up demand and increased online engagement. In 2024, the market is valued at USD 78,500 Million, reflecting sustained consumer interest in premium goods and experiences. Looking ahead, the market is projected to reach USD 135,200 Million by 2033, expanding at a Compound Annual Growth Rate (CAGR) of 6.2% from 2026 to 2033. Key valuation shifts include a noticeable acceleration in digital sales post-2020 and a pivot towards more susta" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/glass-door-merchandiser-market-52924" display="&lt;h2&gt;Glass Door Merchandiser Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 12.5 Billion · Forecast (2033): USD 23.8 Billion · CAGR: 9.5%  &lt;h2&gt;Glass Door Merchandiser Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Glass Door Merchandiser Market encompasses the manufacturing, distribution, and sales of refrigerated display units featuring transparent glass doors, designed to showcase products while maintaining optimal temperature. These units are crucial across various sectors, primarily retail, food service, and increasingly, healthcare. Their current relevance stems from their dual function: preserving perishable goods and enhancing product visibility, thereby driving impulse purchases. The industry has witnessed significant technological evolution, moving from basic refrigeration to advanced solutions incorporating LED lighting, energy-efficient compressors, and smart connectivity. This evolution addresses growing demands for sustainability and operational efficiency. End-use significance is profound, as these merchandisers are indispensable for supermarkets, convenience stores, restaurants, and pharmacies to effectively present beverages, dairy products, frozen foods, and pharmaceuticals, directly influencing consumer buying behavior and inventory management.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/glass-door-merchandiser-market-52924&lt;/h2&gt;  &lt;h2&gt;Glass Door Merchandiser Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Glass Door Merchandiser Market has demonstrated robust historical performance, expanding steadily from an estimated USD 8.1 billion in 2019 to reach a significant valuation of USD 12.5 billion in 2024. This growth trajectory, despite a temporary slowdown in 2020 due to global economic disruptions, reflects the essential role these units play in modern retail and food service. The market quickly rebounded, driven by renewed investments in cold chain infrastructure and retail modernization. The 2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C4" r:id="rId3" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/banquet-cabinet-market-52248" display="&lt;h2&gt;Banquet Cabinet Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 480 Million · Forecast (2033): USD 885 Million · CAGR: 6.8%  &lt;h2&gt;Banquet Cabinet Market Industry Overview&lt;/h2&gt; &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The banquet cabinet market encompasses specialized, insulated mobile units designed for the safe and efficient holding, transport, and serving of food at precise temperatures. These essential pieces of equipment are critical in maintaining food quality, safety, and operational efficiency across various food service sectors. The industry context is deeply rooted in the hospitality, catering, and institutional food service sectors, where large-scale food preparation and distribution are commonplace. Current relevance is driven by the increasing demand for high-quality, safe, and efficiently delivered food experiences in events, healthcare, education, and corporate settings. Technological evolution in this market has seen a shift from basic heated or refrigerated boxes to advanced units featuring precise digital temperature controls, energy-efficient insulation, and even smart connectivity. Their end-use significance lies in ensuring that food, once prepared, reaches its consumption point in optimal condition, preserving taste, texture, and nutritional value, while adhering to stringent food safety standards.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/banquet-cabinet-market-52248&lt;/h2&gt;  &lt;h2&gt;Banquet Cabinet Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The banquet cabinet market has demonstrated a resilient growth trajectory over the past few years. Historically, from 2019 to 2024, the market experienced steady expansion, primarily fueled by the burgeoning global hospitality sector and the increasing frequency of large-scale events. A temporary dip was observed during the initial phases of the COVID-19 pandemic (2020-2021) due to restrictions on gatherings and a slowdown in the hospitality industry. However, a robust recovery foll" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C5" r:id="rId4" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/recycled-denim-market-51572" display="&lt;h2&gt;Recycled Denim Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 480 Million · Forecast (2033): USD 1050 Million · CAGR: 9.0%  &lt;h2&gt;Recycled Denim Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Recycled Denim Market encompasses the entire value chain involved in transforming post-consumer and post-industrial denim waste into new textile fibers, yarns, fabrics, and other products. This burgeoning industry is a critical component of the circular economy, addressing the massive environmental footprint of conventional denim production, which is resource-intensive regarding water, energy, and chemicals. Its current relevance is amplified by global sustainability mandates, increasing consumer awareness, and brand commitments towards eco-friendly practices. Technologically, the market has evolved from rudimentary mechanical shredding to sophisticated processes including advanced mechanical recycling for shorter fibers, and chemical recycling techniques that break down cellulose to produce virgin-like fibers. End-use significance extends beyond new apparel to insulation, furniture stuffing, automotive composites, and non-woven applications, showcasing the versatility and growing demand for sustainable material solutions across various sectors.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/recycled-denim-market-51572&lt;/h2&gt;  &lt;h2&gt;Recycled Denim Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Recycled Denim Market has demonstrated a robust growth trajectory over the past few years, driven by increasing environmental consciousness and industry-wide shifts towards sustainable practices. Historically, from 2019 to 2024, the market experienced steady expansion, albeit with a temporary slowdown in 2020 due to global supply chain disruptions caused by the pandemic. However, a strong recovery and accelerated growth were observed from late 2021 onwards, as brands recommitted to sustainability goals and technological advancements impr" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C6" r:id="rId5" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/global-food-sensory-analysis-service-market-50896" display="&lt;h2&gt;Global Food Sensory Analysis Service Market Size, Strategic Opportunities &amp; Forecast (2026-2033) Market size (2024): USD 485 Million · Forecast (2033): USD 1050 Million · CAGR: 9.0%&lt;/h2&gt;  &lt;h2&gt;Global Food Sensory Analysis Service Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Global Food Sensory Analysis Service Market encompasses specialized services dedicated to evaluating food products based on human senses – sight, smell, taste, touch, and hearing. This scientific discipline is crucial for understanding consumer preferences, ensuring product quality, and driving innovation within the food and beverage industry. Its current relevance is amplified by evolving consumer demands for novel flavors, healthier options, and consistent quality, alongside a growing focus on product differentiation in a competitive landscape. Technologically, the field is evolving beyond traditional human panels, integrating advanced statistical methods, instrumental analysis, and increasingly, AI and machine learning to interpret complex sensory data. End-use significance spans the entire product lifecycle, from initial concept development and ingredient sourcing to quality control, shelf-life studies, and market positioning, playing a pivotal role in consumer acceptance and brand success.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/global-food-sensory-analysis-service-market-50896&lt;/h2&gt;  &lt;h2&gt;Global Food Sensory Analysis Service Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Global Food Sensory Analysis Service Market has demonstrated robust growth over the past few years, reflecting the increasing strategic importance of sensory insights for food and beverage companies. Historically, from 2019 to 2024, the market experienced consistent expansion, driven by heightened consumer expectations for product quality and innovation, alongside stricter regulatory frameworks for food safety and labeling. This period saw a steady uptake of professional sensory services as manufacture" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="C7" r:id="rId6" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/baby-clothing-market-50220" display="&lt;h2&gt;Baby Clothing Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 62.5 Billion · Forecast (2033): USD 105.0 Billion · CAGR: 6.0%  &lt;h2&gt;Baby Clothing Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The baby clothing market encompasses a vast array of garments designed specifically for infants and toddlers, typically from newborn to 36 months of age. This includes everything from bodysuits, sleepwear, outerwear, and dresses to specialized items like organic apparel and smart clothing. The industry is fundamentally driven by birth rates, evolving parental preferences, and increasing disposable incomes globally. Its current relevance is underscored by a growing emphasis on safety, comfort, and sustainability, transforming it from a purely functional market into one deeply intertwined with lifestyle choices and brand values. Technological evolution, while subtle in garment design, manifests in advanced material science for enhanced breathability and hypoallergenic properties, as well as in digital retail and supply chain optimization. End-use significance extends beyond basic necessity, with baby clothing often serving as a means of expression, a gift item, and a reflection of cultural trends and parental aspirations.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/baby-clothing-market-50220&lt;/h2&gt;  &lt;h2&gt;Baby Clothing Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The baby clothing market has demonstrated consistent growth, reflecting stable birth rates and evolving consumer spending patterns. Historically, from 2019 to 2024, the market experienced a steady upward trajectory, driven by increasing awareness of product quality, safety standards, and the rise of e-commerce platforms. Despite minor fluctuations influenced by global economic shifts, the market maintained resilience. In 2024, the global baby clothing market reached an estimated valuation of USD 62.5 Billion, marking a significant milestone in its expansion. Looking ahead," xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="C8" r:id="rId7" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/cell-apoptosis-assay-services-market-49544" display="&lt;h2&gt;Cell Apoptosis Assay Services Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 485 Million · Forecast (2033): USD 1250 Million · CAGR: 11.2%  &lt;h2&gt;Cell Apoptosis Assay Services Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Cell Apoptosis Assay Services Market encompasses specialized laboratory services that quantify and characterize programmed cell death (apoptosis) in biological samples. These services are crucial for drug discovery, toxicology screening, disease research, and understanding fundamental biological processes. Apoptosis, a highly regulated cellular process, is vital for development, tissue homeostasis, and eliminating damaged or unwanted cells. Dysregulation of apoptosis is implicated in numerous diseases, including cancer, neurodegenerative disorders, and autoimmune conditions, making its precise measurement indispensable. The industry's current relevance is underscored by the increasing complexity of therapeutic development, where understanding drug-induced apoptosis is a key determinant of efficacy and safety. Technological evolution, particularly in high-throughput screening, advanced imaging, and multi-parametric analysis, has significantly enhanced the capabilities and efficiency of these services. End-use significance spans pharmaceutical and biotechnology companies, academic research institutions, and contract research organizations (CROs) seeking robust and reliable data for their research and development pipelines.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/cell-apoptosis-assay-services-market-49544&lt;/h2&gt;  &lt;h2&gt;Cell Apoptosis Assay Services Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Cell Apoptosis Assay Services Market has demonstrated robust growth over the past few years, driven by escalating R&amp;D investments in life sciences and a deeper understanding of apoptosis's role in disease pathogenesis. Historically, from 2019 to 2024, the market experienced consistent expansion, with a" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="C9" r:id="rId8" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/global-road-wrecker-market-48868" display="&lt;h2&gt;Global Road Wrecker Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; The Global Road Wrecker Market is poised for steady expansion, driven by infrastructure development and fleet modernization. Market size (2024): USD 385 Million Forecast (2033): USD 620 Million CAGR: 7.0%  &lt;h2&gt;Global Road Wrecker Market Industry Overview&lt;/h2&gt; &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Global Road Wrecker Market encompasses the manufacturing, distribution, and servicing of specialized vehicles designed for towing, recovery, and roadside assistance of disabled or damaged vehicles. These crucial assets, often known as tow trucks or recovery vehicles, range from light-duty units for passenger cars to heavy-duty rotators capable of uprighting overturned commercial trucks and buses. The industry's context is deeply intertwined with global transportation infrastructure, road safety regulations, and the increasing volume of commercial and private vehicles. Its current relevance is amplified by the need for efficient incident management, minimizing traffic disruptions, and ensuring public safety on roadways. Technological evolution, particularly in hydraulic systems, remote diagnostics, and advanced material science, continues to enhance wrecker capabilities and operational efficiency. End-use significance spans government agencies, emergency services, private towing companies, and logistics operators, all relying on these specialized vehicles for critical recovery operations.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/global-road-wrecker-market-48868&lt;/h2&gt;  &lt;h2&gt;Global Road Wrecker Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Global Road Wrecker Market demonstrated resilient historical performance, navigating economic fluctuations and evolving infrastructure demands. From 2019 to 2024, the market experienced consistent growth, albeit with minor dips during periods of global economic uncertainty and supply chain disruptions. The 2024 valuation stands at USD 385 Million, reflecting " xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="C10" r:id="rId9" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/halal-nutraceuticals-and-vaccines-market-48192" display="&lt;h2&gt;Halal Nutraceuticals &amp; Vaccines Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 1800 Million · Forecast (2033): USD 5500 Million · CAGR: 13.2%  &lt;h2&gt;Halal Nutraceuticals &amp; Vaccines Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Halal Nutraceuticals &amp; Vaccines Market encompasses health-promoting products, including dietary supplements, functional foods, and pharmaceutical-grade vaccines, meticulously manufactured and certified to adhere to Islamic dietary and lifestyle laws (Sharia). This means all ingredients, processing aids, manufacturing processes, and packaging must be free from porcine-derived products, alcohol, and other impermissible substances. The industry's context is rooted in the global Muslim population's increasing demand for products that align with their faith, extending beyond food to health and wellness. Current relevance is amplified by rising health consciousness, coupled with a desire for ethical and transparent sourcing. Technological evolution plays a crucial role in ensuring ingredient traceability, advanced analytical testing for contaminants, and innovative formulation techniques that comply with halal standards. The end-use significance spans across various sectors, from daily dietary supplements and specialized functional foods to critical life-saving vaccines, ensuring Muslim consumers have access to permissible and safe health solutions.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/halal-nutraceuticals-and-vaccines-market-48192&lt;/h2&gt;  &lt;h2&gt;Halal Nutraceuticals &amp; Vaccines Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Halal Nutraceuticals &amp; Vaccines Market has demonstrated robust historical performance, driven by increasing global Muslim consumer awareness and a growing emphasis on ethical consumption. From 2019 to 2024, the market experienced steady expansion, as more manufacturers sought halal certification for their products to tap into this underserved demographic. This period s" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="C11" r:id="rId10" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/baby-vitamins-and-supplements-market-47516" display="&lt;h2&gt;Baby Vitamins And Supplements Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 5.8 Billion · Forecast (2033): USD 10.5 Billion · CAGR: 7.2%  &lt;h2&gt;Baby Vitamins And Supplements Market Industry Overview&lt;/h2&gt; &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Baby Vitamins and Supplements Market encompasses a diverse range of nutritional products designed to support the healthy growth and development of infants and toddlers. This includes essential vitamins like D and A, minerals such as iron and zinc, and specialized supplements like probiotics and Omega-3 fatty acids. The industry's current relevance is driven by increasing parental awareness regarding nutritional gaps, the rise in pediatric recommendations for specific supplements, and a global focus on preventative health from an early age. Technological evolution is evident in advanced formulations, improved delivery methods like drops and chewables, and the development of more palatable options. These products are crucial for addressing dietary deficiencies, supporting immune function, aiding cognitive development, and ensuring overall well-being in the critical early years of life.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/baby-vitamins-and-supplements-market-47516&lt;/h2&gt;  &lt;h2&gt;Baby Vitamins And Supplements Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Baby Vitamins and Supplements Market has demonstrated robust historical performance, experiencing consistent growth from 2019 to 2024, largely fueled by heightened health consciousness and product innovation. The market was valued at USD 5.8 Billion in 2024, reflecting a steady upward trajectory despite global economic fluctuations. Looking ahead, the market is projected to reach USD 10.5 Billion by 2033, exhibiting a compelling Compound Annual Growth Rate (CAGR) of 7.2% from 2026 to 2033. Key valuation shifts have been influenced by increasing disposable incomes, a global birth rate rebound in certain regions, and a growing preference for n" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C2" r:id="rId1" display="&lt;h2&gt;Luxury Clothes Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 78,500 Million · Forecast (2033): USD 135,200 Million · CAGR: 6.2%  &lt;h2&gt;Luxury Clothes Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Luxury Clothes Market encompasses high-end apparel and accessories characterized by superior craftsmanship, exclusive designs, premium materials, and brand prestige. This sector caters to discerning consumers seeking exclusivity, quality, and status. Its current relevance is amplified by rising disposable incomes globally, particularly in emerging economies, and a growing consumer appreciation for sustainable and ethically produced goods. Technological evolution, including advanced manufacturing techniques and digital design, is enhancing product innovation and customization. End-use significance extends beyond personal adornment, influencing fashion trends, cultural expression, and serving as an investment for some consumers. The market thrives on brand heritage, aspirational marketing, and an evolving definition of luxury that now often includes digital and experiential elements.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/luxury-clothes-market-53600&lt;/h2&gt;  &lt;h2&gt;Luxury Clothes Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Luxury Clothes Market has demonstrated robust historical performance, navigating global economic shifts with resilience. From 2019 to 2024, the market experienced steady growth, punctuated by a brief dip during the pandemic, followed by a strong rebound driven by pent-up demand and increased online engagement. In 2024, the market is valued at USD 78,500 Million, reflecting sustained consumer interest in premium goods and experiences. Looking ahead, the market is projected to reach USD 135,200 Million by 2033, expanding at a Compound Annual Growth Rate (CAGR) of 6.2% from 2026 to 2033. Key valuation shifts include a noticeable acceleration in digital sales post-2020 and a pivot towards more susta" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/luxury-clothes-market-53600"/>
+    <hyperlink ref="C3" r:id="rId2" display="&lt;h2&gt;Glass Door Merchandiser Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 12.5 Billion · Forecast (2033): USD 23.8 Billion · CAGR: 9.5%  &lt;h2&gt;Glass Door Merchandiser Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Glass Door Merchandiser Market encompasses the manufacturing, distribution, and sales of refrigerated display units featuring transparent glass doors, designed to showcase products while maintaining optimal temperature. These units are crucial across various sectors, primarily retail, food service, and increasingly, healthcare. Their current relevance stems from their dual function: preserving perishable goods and enhancing product visibility, thereby driving impulse purchases. The industry has witnessed significant technological evolution, moving from basic refrigeration to advanced solutions incorporating LED lighting, energy-efficient compressors, and smart connectivity. This evolution addresses growing demands for sustainability and operational efficiency. End-use significance is profound, as these merchandisers are indispensable for supermarkets, convenience stores, restaurants, and pharmacies to effectively present beverages, dairy products, frozen foods, and pharmaceuticals, directly influencing consumer buying behavior and inventory management.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/glass-door-merchandiser-market-52924&lt;/h2&gt;  &lt;h2&gt;Glass Door Merchandiser Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Glass Door Merchandiser Market has demonstrated robust historical performance, expanding steadily from an estimated USD 8.1 billion in 2019 to reach a significant valuation of USD 12.5 billion in 2024. This growth trajectory, despite a temporary slowdown in 2020 due to global economic disruptions, reflects the essential role these units play in modern retail and food service. The market quickly rebounded, driven by renewed investments in cold chain infrastructure and retail modernization. The 2" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/glass-door-merchandiser-market-52924"/>
+    <hyperlink ref="C4" r:id="rId3" display="&lt;h2&gt;Banquet Cabinet Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 480 Million · Forecast (2033): USD 885 Million · CAGR: 6.8%  &lt;h2&gt;Banquet Cabinet Market Industry Overview&lt;/h2&gt; &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The banquet cabinet market encompasses specialized, insulated mobile units designed for the safe and efficient holding, transport, and serving of food at precise temperatures. These essential pieces of equipment are critical in maintaining food quality, safety, and operational efficiency across various food service sectors. The industry context is deeply rooted in the hospitality, catering, and institutional food service sectors, where large-scale food preparation and distribution are commonplace. Current relevance is driven by the increasing demand for high-quality, safe, and efficiently delivered food experiences in events, healthcare, education, and corporate settings. Technological evolution in this market has seen a shift from basic heated or refrigerated boxes to advanced units featuring precise digital temperature controls, energy-efficient insulation, and even smart connectivity. Their end-use significance lies in ensuring that food, once prepared, reaches its consumption point in optimal condition, preserving taste, texture, and nutritional value, while adhering to stringent food safety standards.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/banquet-cabinet-market-52248&lt;/h2&gt;  &lt;h2&gt;Banquet Cabinet Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The banquet cabinet market has demonstrated a resilient growth trajectory over the past few years. Historically, from 2019 to 2024, the market experienced steady expansion, primarily fueled by the burgeoning global hospitality sector and the increasing frequency of large-scale events. A temporary dip was observed during the initial phases of the COVID-19 pandemic (2020-2021) due to restrictions on gatherings and a slowdown in the hospitality industry. However, a robust recovery foll" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/banquet-cabinet-market-52248"/>
+    <hyperlink ref="C5" r:id="rId4" display="&lt;h2&gt;Recycled Denim Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 480 Million · Forecast (2033): USD 1050 Million · CAGR: 9.0%  &lt;h2&gt;Recycled Denim Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Recycled Denim Market encompasses the entire value chain involved in transforming post-consumer and post-industrial denim waste into new textile fibers, yarns, fabrics, and other products. This burgeoning industry is a critical component of the circular economy, addressing the massive environmental footprint of conventional denim production, which is resource-intensive regarding water, energy, and chemicals. Its current relevance is amplified by global sustainability mandates, increasing consumer awareness, and brand commitments towards eco-friendly practices. Technologically, the market has evolved from rudimentary mechanical shredding to sophisticated processes including advanced mechanical recycling for shorter fibers, and chemical recycling techniques that break down cellulose to produce virgin-like fibers. End-use significance extends beyond new apparel to insulation, furniture stuffing, automotive composites, and non-woven applications, showcasing the versatility and growing demand for sustainable material solutions across various sectors.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/recycled-denim-market-51572&lt;/h2&gt;  &lt;h2&gt;Recycled Denim Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Recycled Denim Market has demonstrated a robust growth trajectory over the past few years, driven by increasing environmental consciousness and industry-wide shifts towards sustainable practices. Historically, from 2019 to 2024, the market experienced steady expansion, albeit with a temporary slowdown in 2020 due to global supply chain disruptions caused by the pandemic. However, a strong recovery and accelerated growth were observed from late 2021 onwards, as brands recommitted to sustainability goals and technological advancements impr" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/recycled-denim-market-51572"/>
+    <hyperlink ref="C6" r:id="rId5" display="&lt;h2&gt;Global Food Sensory Analysis Service Market Size, Strategic Opportunities &amp; Forecast (2026-2033) Market size (2024): USD 485 Million · Forecast (2033): USD 1050 Million · CAGR: 9.0%&lt;/h2&gt;  &lt;h2&gt;Global Food Sensory Analysis Service Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Global Food Sensory Analysis Service Market encompasses specialized services dedicated to evaluating food products based on human senses – sight, smell, taste, touch, and hearing. This scientific discipline is crucial for understanding consumer preferences, ensuring product quality, and driving innovation within the food and beverage industry. Its current relevance is amplified by evolving consumer demands for novel flavors, healthier options, and consistent quality, alongside a growing focus on product differentiation in a competitive landscape. Technologically, the field is evolving beyond traditional human panels, integrating advanced statistical methods, instrumental analysis, and increasingly, AI and machine learning to interpret complex sensory data. End-use significance spans the entire product lifecycle, from initial concept development and ingredient sourcing to quality control, shelf-life studies, and market positioning, playing a pivotal role in consumer acceptance and brand success.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/global-food-sensory-analysis-service-market-50896&lt;/h2&gt;  &lt;h2&gt;Global Food Sensory Analysis Service Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Global Food Sensory Analysis Service Market has demonstrated robust growth over the past few years, reflecting the increasing strategic importance of sensory insights for food and beverage companies. Historically, from 2019 to 2024, the market experienced consistent expansion, driven by heightened consumer expectations for product quality and innovation, alongside stricter regulatory frameworks for food safety and labeling. This period saw a steady uptake of professional sensory services as manufacture" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/global-food-sensory-analysis-service-market-50896"/>
+    <hyperlink ref="C7" r:id="rId6" display="&lt;h2&gt;Baby Clothing Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 62.5 Billion · Forecast (2033): USD 105.0 Billion · CAGR: 6.0%  &lt;h2&gt;Baby Clothing Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The baby clothing market encompasses a vast array of garments designed specifically for infants and toddlers, typically from newborn to 36 months of age. This includes everything from bodysuits, sleepwear, outerwear, and dresses to specialized items like organic apparel and smart clothing. The industry is fundamentally driven by birth rates, evolving parental preferences, and increasing disposable incomes globally. Its current relevance is underscored by a growing emphasis on safety, comfort, and sustainability, transforming it from a purely functional market into one deeply intertwined with lifestyle choices and brand values. Technological evolution, while subtle in garment design, manifests in advanced material science for enhanced breathability and hypoallergenic properties, as well as in digital retail and supply chain optimization. End-use significance extends beyond basic necessity, with baby clothing often serving as a means of expression, a gift item, and a reflection of cultural trends and parental aspirations.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/baby-clothing-market-50220&lt;/h2&gt;  &lt;h2&gt;Baby Clothing Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The baby clothing market has demonstrated consistent growth, reflecting stable birth rates and evolving consumer spending patterns. Historically, from 2019 to 2024, the market experienced a steady upward trajectory, driven by increasing awareness of product quality, safety standards, and the rise of e-commerce platforms. Despite minor fluctuations influenced by global economic shifts, the market maintained resilience. In 2024, the global baby clothing market reached an estimated valuation of USD 62.5 Billion, marking a significant milestone in its expansion. Looking ahead," tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/baby-clothing-market-50220"/>
+    <hyperlink ref="C8" r:id="rId7" display="&lt;h2&gt;Cell Apoptosis Assay Services Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 485 Million · Forecast (2033): USD 1250 Million · CAGR: 11.2%  &lt;h2&gt;Cell Apoptosis Assay Services Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Cell Apoptosis Assay Services Market encompasses specialized laboratory services that quantify and characterize programmed cell death (apoptosis) in biological samples. These services are crucial for drug discovery, toxicology screening, disease research, and understanding fundamental biological processes. Apoptosis, a highly regulated cellular process, is vital for development, tissue homeostasis, and eliminating damaged or unwanted cells. Dysregulation of apoptosis is implicated in numerous diseases, including cancer, neurodegenerative disorders, and autoimmune conditions, making its precise measurement indispensable. The industry's current relevance is underscored by the increasing complexity of therapeutic development, where understanding drug-induced apoptosis is a key determinant of efficacy and safety. Technological evolution, particularly in high-throughput screening, advanced imaging, and multi-parametric analysis, has significantly enhanced the capabilities and efficiency of these services. End-use significance spans pharmaceutical and biotechnology companies, academic research institutions, and contract research organizations (CROs) seeking robust and reliable data for their research and development pipelines.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/cell-apoptosis-assay-services-market-49544&lt;/h2&gt;  &lt;h2&gt;Cell Apoptosis Assay Services Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Cell Apoptosis Assay Services Market has demonstrated robust growth over the past few years, driven by escalating R&amp;D investments in life sciences and a deeper understanding of apoptosis's role in disease pathogenesis. Historically, from 2019 to 2024, the market experienced consistent expansion, with a" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/cell-apoptosis-assay-services-market-49544"/>
+    <hyperlink ref="C9" r:id="rId8" display="&lt;h2&gt;Global Road Wrecker Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; The Global Road Wrecker Market is poised for steady expansion, driven by infrastructure development and fleet modernization. Market size (2024): USD 385 Million Forecast (2033): USD 620 Million CAGR: 7.0%  &lt;h2&gt;Global Road Wrecker Market Industry Overview&lt;/h2&gt; &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Global Road Wrecker Market encompasses the manufacturing, distribution, and servicing of specialized vehicles designed for towing, recovery, and roadside assistance of disabled or damaged vehicles. These crucial assets, often known as tow trucks or recovery vehicles, range from light-duty units for passenger cars to heavy-duty rotators capable of uprighting overturned commercial trucks and buses. The industry's context is deeply intertwined with global transportation infrastructure, road safety regulations, and the increasing volume of commercial and private vehicles. Its current relevance is amplified by the need for efficient incident management, minimizing traffic disruptions, and ensuring public safety on roadways. Technological evolution, particularly in hydraulic systems, remote diagnostics, and advanced material science, continues to enhance wrecker capabilities and operational efficiency. End-use significance spans government agencies, emergency services, private towing companies, and logistics operators, all relying on these specialized vehicles for critical recovery operations.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/global-road-wrecker-market-48868&lt;/h2&gt;  &lt;h2&gt;Global Road Wrecker Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Global Road Wrecker Market demonstrated resilient historical performance, navigating economic fluctuations and evolving infrastructure demands. From 2019 to 2024, the market experienced consistent growth, albeit with minor dips during periods of global economic uncertainty and supply chain disruptions. The 2024 valuation stands at USD 385 Million, reflecting " tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/global-road-wrecker-market-48868"/>
+    <hyperlink ref="C10" r:id="rId9" display="&lt;h2&gt;Halal Nutraceuticals &amp; Vaccines Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 1800 Million · Forecast (2033): USD 5500 Million · CAGR: 13.2%  &lt;h2&gt;Halal Nutraceuticals &amp; Vaccines Market Industry Overview&lt;/h2&gt;  &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Halal Nutraceuticals &amp; Vaccines Market encompasses health-promoting products, including dietary supplements, functional foods, and pharmaceutical-grade vaccines, meticulously manufactured and certified to adhere to Islamic dietary and lifestyle laws (Sharia). This means all ingredients, processing aids, manufacturing processes, and packaging must be free from porcine-derived products, alcohol, and other impermissible substances. The industry's context is rooted in the global Muslim population's increasing demand for products that align with their faith, extending beyond food to health and wellness. Current relevance is amplified by rising health consciousness, coupled with a desire for ethical and transparent sourcing. Technological evolution plays a crucial role in ensuring ingredient traceability, advanced analytical testing for contaminants, and innovative formulation techniques that comply with halal standards. The end-use significance spans across various sectors, from daily dietary supplements and specialized functional foods to critical life-saving vaccines, ensuring Muslim consumers have access to permissible and safe health solutions.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/halal-nutraceuticals-and-vaccines-market-48192&lt;/h2&gt;  &lt;h2&gt;Halal Nutraceuticals &amp; Vaccines Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Halal Nutraceuticals &amp; Vaccines Market has demonstrated robust historical performance, driven by increasing global Muslim consumer awareness and a growing emphasis on ethical consumption. From 2019 to 2024, the market experienced steady expansion, as more manufacturers sought halal certification for their products to tap into this underserved demographic. This period s" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/halal-nutraceuticals-and-vaccines-market-48192"/>
+    <hyperlink ref="C11" r:id="rId10" display="&lt;h2&gt;Baby Vitamins And Supplements Market Size, Strategic Opportunities &amp; Forecast (2026-2033)&lt;/h2&gt; Market size (2024): USD 5.8 Billion · Forecast (2033): USD 10.5 Billion · CAGR: 7.2%  &lt;h2&gt;Baby Vitamins And Supplements Market Industry Overview&lt;/h2&gt; &lt;h3&gt;Introduction and Industry Overview&lt;/h3&gt; The Baby Vitamins and Supplements Market encompasses a diverse range of nutritional products designed to support the healthy growth and development of infants and toddlers. This includes essential vitamins like D and A, minerals such as iron and zinc, and specialized supplements like probiotics and Omega-3 fatty acids. The industry's current relevance is driven by increasing parental awareness regarding nutritional gaps, the rise in pediatric recommendations for specific supplements, and a global focus on preventative health from an early age. Technological evolution is evident in advanced formulations, improved delivery methods like drops and chewables, and the development of more palatable options. These products are crucial for addressing dietary deficiencies, supporting immune function, aiding cognitive development, and ensuring overall well-being in the critical early years of life.  &lt;h2&gt;Get the full PDF sample copy of the report: https://datahorizzonresearch.com/request-sample-pdf/baby-vitamins-and-supplements-market-47516&lt;/h2&gt;  &lt;h2&gt;Baby Vitamins And Supplements Market Size, Valuation &amp; Historical Performance&lt;/h2&gt; The Baby Vitamins and Supplements Market has demonstrated robust historical performance, experiencing consistent growth from 2019 to 2024, largely fueled by heightened health consciousness and product innovation. The market was valued at USD 5.8 Billion in 2024, reflecting a steady upward trajectory despite global economic fluctuations. Looking ahead, the market is projected to reach USD 10.5 Billion by 2033, exhibiting a compelling Compound Annual Growth Rate (CAGR) of 7.2% from 2026 to 2033. Key valuation shifts have been influenced by increasing disposable incomes, a global birth rate rebound in certain regions, and a growing preference for n" tooltip="Opens: https://datahorizzonresearch.com/request-sample-pdf/baby-vitamins-and-supplements-market-47516"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>